--- a/client/Public/order conformation Forms/ORDER CONFIRMATION EXCEL.xlsx
+++ b/client/Public/order conformation Forms/ORDER CONFIRMATION EXCEL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JOYAL'S LEGION\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b68409331e52ac1/Documents/GRP/GRP_SYS/client/Public/order conformation Forms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC4025D7-7FB2-4D0C-8609-2F68FE2F2190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{AC4025D7-7FB2-4D0C-8609-2F68FE2F2190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27426115-3028-489A-9784-A09654BFEE87}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="720" windowWidth="19200" windowHeight="11170" xr2:uid="{6E4D5EB5-8919-4098-B3DA-50DFE8F24D7E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{6E4D5EB5-8919-4098-B3DA-50DFE8F24D7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -784,22 +784,11 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="P16:R16"/>
-    <mergeCell ref="P18:R18"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="K11:W11"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="K13:W13"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="P20:R20"/>
-    <mergeCell ref="I22:W22"/>
-    <mergeCell ref="D26:E27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="D31:E32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="P32:R32"/>
+    <mergeCell ref="D36:N36"/>
+    <mergeCell ref="D38:N38"/>
+    <mergeCell ref="C52:N52"/>
+    <mergeCell ref="C54:N54"/>
+    <mergeCell ref="C56:N56"/>
     <mergeCell ref="O70:W70"/>
     <mergeCell ref="O72:W72"/>
     <mergeCell ref="E40:H41"/>
@@ -813,11 +802,22 @@
     <mergeCell ref="C67:N67"/>
     <mergeCell ref="D70:H70"/>
     <mergeCell ref="D72:H72"/>
-    <mergeCell ref="D36:N36"/>
-    <mergeCell ref="D38:N38"/>
-    <mergeCell ref="C52:N52"/>
-    <mergeCell ref="C54:N54"/>
-    <mergeCell ref="C56:N56"/>
+    <mergeCell ref="I22:W22"/>
+    <mergeCell ref="D26:E27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="D31:E32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="P32:R32"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="P16:R16"/>
+    <mergeCell ref="P18:R18"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="K11:W11"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="K13:W13"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="P20:R20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
